--- a/marvelDataBase.xlsx
+++ b/marvelDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53d1950b8098280d/Dokument/Chalmers/Selfstudies/web2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1112" documentId="8_{4A07A081-6370-4A72-BE4F-8096673AA919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97C0DEA8-9377-42B5-9817-E295DEBFAF5A}"/>
+  <xr:revisionPtr revIDLastSave="1189" documentId="8_{4A07A081-6370-4A72-BE4F-8096673AA919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A89FCC24-3D2F-4E8B-8BCA-501AE0DA17A8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8EB36B68-46C3-4C45-AF1B-13B04053E69B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EB36B68-46C3-4C45-AF1B-13B04053E69B}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="254">
   <si>
     <t>Character</t>
   </si>
@@ -705,6 +705,99 @@
   </si>
   <si>
     <t>Iron Man</t>
+  </si>
+  <si>
+    <t>Iron Man 2</t>
+  </si>
+  <si>
+    <t>Thor: Ragnarok</t>
+  </si>
+  <si>
+    <t>The Avengers</t>
+  </si>
+  <si>
+    <t>Guardians of the Galaxy</t>
+  </si>
+  <si>
+    <t>Captain America: The Winter Soldier</t>
+  </si>
+  <si>
+    <t>Avengers: Age of Ultron</t>
+  </si>
+  <si>
+    <t>Ant-Man</t>
+  </si>
+  <si>
+    <t>Captain America: Civil War</t>
+  </si>
+  <si>
+    <t>Doctor Strange</t>
+  </si>
+  <si>
+    <t>Guardians of the Galaxy Vol. 2</t>
+  </si>
+  <si>
+    <t>Captain Aerica: Civil War</t>
+  </si>
+  <si>
+    <t>Spider-Man: Homecoming</t>
+  </si>
+  <si>
+    <t>Captain Marvel</t>
+  </si>
+  <si>
+    <t>Avengers: Endgame</t>
+  </si>
+  <si>
+    <t>Spider-Man: Far From Home</t>
+  </si>
+  <si>
+    <t>Black Panther</t>
+  </si>
+  <si>
+    <t>Black Widow</t>
+  </si>
+  <si>
+    <t>Shang-Chi and the Legend oof the Ten Rings</t>
+  </si>
+  <si>
+    <t>Spider-Man: No Way Home</t>
+  </si>
+  <si>
+    <t>Doctor Strange in the Multiverse of Madness</t>
+  </si>
+  <si>
+    <t>WandaVision</t>
+  </si>
+  <si>
+    <t>Agatha All Along</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>X2: X-Men united</t>
+  </si>
+  <si>
+    <t>X-Men: The Last Stand</t>
+  </si>
+  <si>
+    <t>X-Men Origins: Wolverine</t>
+  </si>
+  <si>
+    <t>Deadpool</t>
+  </si>
+  <si>
+    <t>X-Men: Apocalypse</t>
+  </si>
+  <si>
+    <t>Logan</t>
+  </si>
+  <si>
+    <t>X-Men: Days of Future Past</t>
+  </si>
+  <si>
+    <t>Deadpool &amp; Wolverine</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1180,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="16.21875" customWidth="1"/>
     <col min="9" max="9" width="34.109375" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
     <col min="11" max="11" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1442,6 +1535,9 @@
       <c r="I11" t="s">
         <v>136</v>
       </c>
+      <c r="J11" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1471,6 +1567,9 @@
       <c r="I12" t="s">
         <v>137</v>
       </c>
+      <c r="J12" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1500,6 +1599,9 @@
       <c r="I13" t="s">
         <v>138</v>
       </c>
+      <c r="J13" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1529,6 +1631,9 @@
       <c r="I14" t="s">
         <v>139</v>
       </c>
+      <c r="J14" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1558,6 +1663,9 @@
       <c r="I15" t="s">
         <v>140</v>
       </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1587,8 +1695,11 @@
       <c r="I16" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -1616,8 +1727,11 @@
       <c r="I17" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1645,8 +1759,11 @@
       <c r="I18" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -1674,8 +1791,11 @@
       <c r="I19" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -1703,8 +1823,11 @@
       <c r="I20" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1732,8 +1855,11 @@
       <c r="I21" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1761,8 +1887,11 @@
       <c r="I22" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1790,8 +1919,11 @@
       <c r="I23" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1819,8 +1951,11 @@
       <c r="I24" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1848,8 +1983,11 @@
       <c r="I25" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1877,8 +2015,11 @@
       <c r="I26" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -1906,8 +2047,11 @@
       <c r="I27" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -1935,8 +2079,11 @@
       <c r="I28" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -1964,8 +2111,11 @@
       <c r="I29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -1993,8 +2143,11 @@
       <c r="I30" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2022,8 +2175,11 @@
       <c r="I31" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -2051,8 +2207,11 @@
       <c r="I32" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -2080,8 +2239,11 @@
       <c r="I33" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -2109,8 +2271,11 @@
       <c r="I34" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -2138,8 +2303,11 @@
       <c r="I35" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -2167,8 +2335,11 @@
       <c r="I36" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>57</v>
       </c>
@@ -2196,8 +2367,11 @@
       <c r="I37" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -2225,8 +2399,11 @@
       <c r="I38" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -2254,8 +2431,11 @@
       <c r="I39" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -2283,8 +2463,11 @@
       <c r="I40" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>62</v>
       </c>
@@ -2312,8 +2495,11 @@
       <c r="I41" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>63</v>
       </c>
@@ -2341,8 +2527,11 @@
       <c r="I42" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -2370,8 +2559,11 @@
       <c r="I43" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -2399,8 +2591,11 @@
       <c r="I44" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -2428,8 +2623,11 @@
       <c r="I45" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -2457,8 +2655,11 @@
       <c r="I46" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>115</v>
       </c>
@@ -2486,8 +2687,11 @@
       <c r="I47" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -2515,8 +2719,11 @@
       <c r="I48" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2544,8 +2751,11 @@
       <c r="I49" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -2573,8 +2783,11 @@
       <c r="I50" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -2602,8 +2815,11 @@
       <c r="I51" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +2847,11 @@
       <c r="I52" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -2660,8 +2879,11 @@
       <c r="I53" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2911,11 @@
       <c r="I54" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2943,11 @@
       <c r="I55" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2975,11 @@
       <c r="I56" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3007,11 @@
       <c r="I57" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -2805,8 +3039,11 @@
       <c r="I58" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>79</v>
       </c>
@@ -2834,8 +3071,11 @@
       <c r="I59" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>80</v>
       </c>
@@ -2863,8 +3103,11 @@
       <c r="I60" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -2892,8 +3135,11 @@
       <c r="I61" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -2921,8 +3167,11 @@
       <c r="I62" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -2950,8 +3199,11 @@
       <c r="I63" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>84</v>
       </c>
@@ -2979,8 +3231,11 @@
       <c r="I64" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>85</v>
       </c>
@@ -3008,8 +3263,11 @@
       <c r="I65" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>86</v>
       </c>
@@ -3037,8 +3295,11 @@
       <c r="I66" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>87</v>
       </c>
@@ -3066,8 +3327,11 @@
       <c r="I67" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -3095,8 +3359,11 @@
       <c r="I68" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>89</v>
       </c>
@@ -3124,8 +3391,11 @@
       <c r="I69" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>90</v>
       </c>
@@ -3153,8 +3423,11 @@
       <c r="I70" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>91</v>
       </c>
@@ -3182,8 +3455,11 @@
       <c r="I71" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>92</v>
       </c>
@@ -3211,8 +3487,11 @@
       <c r="I72" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>93</v>
       </c>
@@ -3240,8 +3519,11 @@
       <c r="I73" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J73" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -3269,8 +3551,11 @@
       <c r="I74" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>95</v>
       </c>
@@ -3298,8 +3583,11 @@
       <c r="I75" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>96</v>
       </c>
@@ -3327,8 +3615,11 @@
       <c r="I76" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>119</v>
       </c>
@@ -3356,8 +3647,11 @@
       <c r="I77" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J77" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -3385,8 +3679,11 @@
       <c r="I78" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J78" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -3414,8 +3711,11 @@
       <c r="I79" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>99</v>
       </c>
@@ -3443,8 +3743,11 @@
       <c r="I80" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -3472,8 +3775,11 @@
       <c r="I81" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -3501,8 +3807,11 @@
       <c r="I82" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>102</v>
       </c>
@@ -3530,8 +3839,11 @@
       <c r="I83" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>103</v>
       </c>
@@ -3559,8 +3871,11 @@
       <c r="I84" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>104</v>
       </c>
@@ -3588,8 +3903,11 @@
       <c r="I85" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>105</v>
       </c>
@@ -3617,8 +3935,11 @@
       <c r="I86" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>106</v>
       </c>
@@ -3646,8 +3967,11 @@
       <c r="I87" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>120</v>
       </c>
@@ -3675,8 +3999,11 @@
       <c r="I88" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J88" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>126</v>
       </c>
@@ -3704,8 +4031,11 @@
       <c r="I89" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>56</v>
       </c>
@@ -3733,8 +4063,11 @@
       <c r="I90" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J90" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -3762,8 +4095,11 @@
       <c r="I91" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J91" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>123</v>
       </c>
@@ -3791,8 +4127,11 @@
       <c r="I92" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J92" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>124</v>
       </c>
@@ -3819,6 +4158,9 @@
       </c>
       <c r="I93" t="s">
         <v>218</v>
+      </c>
+      <c r="J93" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
